--- a/Zaloga_Avtomatizirana.xlsx
+++ b/Zaloga_Avtomatizirana.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\KalkulacijaPetric\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DARKO\KalkulacijaPetric\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD0422D-428B-44A6-807C-C94BA5CDD52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19485" windowHeight="10695"/>
+    <workbookView xWindow="780" yWindow="375" windowWidth="21600" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TRENUTNA ZALOGA" sheetId="1" r:id="rId1"/>
     <sheet name="PRISPELO" sheetId="2" r:id="rId2"/>
     <sheet name="ODPIS" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -2699,7 +2700,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2713,11 +2714,15 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2756,7 +2761,52 @@
   <cellStyles count="1">
     <cellStyle name="Navadno" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1E3A8A"/>
+          <bgColor rgb="FF1E3A8A"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2774,6 +2824,181 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A1EC165-9B78-4B71-92EE-511DAC593CD9}" name="Tabela1" displayName="Tabela1" ref="A1:I2272" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:I2272" xr:uid="{3A1EC165-9B78-4B71-92EE-511DAC593CD9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="100"/>
+        <filter val="101"/>
+        <filter val="102"/>
+        <filter val="110"/>
+        <filter val="114"/>
+        <filter val="125"/>
+        <filter val="126"/>
+        <filter val="160"/>
+        <filter val="162"/>
+        <filter val="210"/>
+        <filter val="220"/>
+        <filter val="229"/>
+        <filter val="32,4"/>
+        <filter val="33,2"/>
+        <filter val="33,8"/>
+        <filter val="34,8"/>
+        <filter val="35"/>
+        <filter val="35,6"/>
+        <filter val="36,5"/>
+        <filter val="42"/>
+        <filter val="43"/>
+        <filter val="43,8"/>
+        <filter val="44,8"/>
+        <filter val="45"/>
+        <filter val="46"/>
+        <filter val="48"/>
+        <filter val="49,8"/>
+        <filter val="50"/>
+        <filter val="50,5"/>
+        <filter val="50,8"/>
+        <filter val="51,8"/>
+        <filter val="52"/>
+        <filter val="55"/>
+        <filter val="56"/>
+        <filter val="57"/>
+        <filter val="59"/>
+        <filter val="59,8"/>
+        <filter val="61"/>
+        <filter val="61,5"/>
+        <filter val="63"/>
+        <filter val="63,5"/>
+        <filter val="63,8"/>
+        <filter val="64"/>
+        <filter val="64,1"/>
+        <filter val="65"/>
+        <filter val="68"/>
+        <filter val="68,4"/>
+        <filter val="69,8"/>
+        <filter val="70"/>
+        <filter val="70,5"/>
+        <filter val="70,7"/>
+        <filter val="700"/>
+        <filter val="71"/>
+        <filter val="72"/>
+        <filter val="720"/>
+        <filter val="73"/>
+        <filter val="74"/>
+        <filter val="75"/>
+        <filter val="85"/>
+        <filter val="86"/>
+        <filter val="88"/>
+        <filter val="90"/>
+        <filter val="92"/>
+        <filter val="93"/>
+        <filter val="93,6"/>
+        <filter val="99,8"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="100"/>
+        <filter val="101"/>
+        <filter val="102"/>
+        <filter val="103"/>
+        <filter val="103,2"/>
+        <filter val="104"/>
+        <filter val="106"/>
+        <filter val="110"/>
+        <filter val="126"/>
+        <filter val="130"/>
+        <filter val="160"/>
+        <filter val="162"/>
+        <filter val="176"/>
+        <filter val="229"/>
+        <filter val="230"/>
+        <filter val="297"/>
+        <filter val="31,8"/>
+        <filter val="32"/>
+        <filter val="324"/>
+        <filter val="33,2"/>
+        <filter val="34,8"/>
+        <filter val="35"/>
+        <filter val="35,8"/>
+        <filter val="39,8"/>
+        <filter val="42"/>
+        <filter val="42,2"/>
+        <filter val="42,5"/>
+        <filter val="43"/>
+        <filter val="43,8"/>
+        <filter val="44"/>
+        <filter val="44,2"/>
+        <filter val="44,8"/>
+        <filter val="45"/>
+        <filter val="46"/>
+        <filter val="47,8"/>
+        <filter val="48"/>
+        <filter val="49,8"/>
+        <filter val="50"/>
+        <filter val="50,8"/>
+        <filter val="51"/>
+        <filter val="51,5"/>
+        <filter val="52"/>
+        <filter val="53"/>
+        <filter val="53,5"/>
+        <filter val="55"/>
+        <filter val="56"/>
+        <filter val="57"/>
+        <filter val="61"/>
+        <filter val="62,8"/>
+        <filter val="63"/>
+        <filter val="63,8"/>
+        <filter val="64"/>
+        <filter val="65"/>
+        <filter val="66"/>
+        <filter val="68"/>
+        <filter val="69,6"/>
+        <filter val="69,8"/>
+        <filter val="70"/>
+        <filter val="70,7"/>
+        <filter val="700"/>
+        <filter val="71"/>
+        <filter val="71,5"/>
+        <filter val="71,8"/>
+        <filter val="72"/>
+        <filter val="720"/>
+        <filter val="73"/>
+        <filter val="73,3"/>
+        <filter val="74,5"/>
+        <filter val="86"/>
+        <filter val="87"/>
+        <filter val="88"/>
+        <filter val="89,9"/>
+        <filter val="90"/>
+        <filter val="92"/>
+        <filter val="96"/>
+        <filter val="97"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{D98DA494-1544-4588-8474-008577444B25}" name="Šifra materiala"/>
+    <tableColumn id="2" xr3:uid="{7881A61B-04B9-4AFA-B154-503E6EECEEF8}" name="Naziv materiala"/>
+    <tableColumn id="3" xr3:uid="{125582EF-D0E8-4A72-BB69-6DA4F1B1F544}" name="Širina"/>
+    <tableColumn id="4" xr3:uid="{D996FB00-8F96-4ECE-A09D-712676C60392}" name="Višina"/>
+    <tableColumn id="5" xr3:uid="{DC2FA5BE-866D-4A87-AF90-B58FB3E01BC3}" name="Gramatura"/>
+    <tableColumn id="6" xr3:uid="{173E23C4-248E-4748-9014-3717813EC073}" name="Začetna zaloga"/>
+    <tableColumn id="7" xr3:uid="{62721AEB-03B1-47B4-9088-6B52ECFD0807}" name="Skupaj Prispelo">
+      <calculatedColumnFormula>SUMIF(PRISPELO!B:B, A2, PRISPELO!D:D)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{3D03000F-A7F0-4061-86E6-2D7B91C561AB}" name="Skupaj Odpisano">
+      <calculatedColumnFormula>SUMIF(ODPIS!B:B, A2, ODPIS!D:D)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{91690EE8-03A4-49BB-AFC3-BF4ABE771C78}" name="TRENUTNA ZALOGA" dataDxfId="1">
+      <calculatedColumnFormula>F2 + G2 - H2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3038,13 +3263,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2272"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="9" width="15" customWidth="1"/>
+    <col min="3" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5380,7 +5609,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1983</v>
       </c>
@@ -5412,7 +5641,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1984</v>
       </c>
@@ -5444,7 +5673,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1988</v>
       </c>
@@ -5476,7 +5705,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1991</v>
       </c>
@@ -5508,7 +5737,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1993</v>
       </c>
@@ -5540,7 +5769,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1994</v>
       </c>
@@ -5572,7 +5801,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1995</v>
       </c>
@@ -5604,7 +5833,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1997</v>
       </c>
@@ -5636,7 +5865,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1999</v>
       </c>
@@ -5668,7 +5897,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2003</v>
       </c>
@@ -5700,7 +5929,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1985</v>
       </c>
@@ -5732,7 +5961,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2013</v>
       </c>
@@ -5860,7 +6089,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1989</v>
       </c>
@@ -5892,7 +6121,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2007</v>
       </c>
@@ -5956,7 +6185,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2032</v>
       </c>
@@ -6148,7 +6377,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2005</v>
       </c>
@@ -6212,7 +6441,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2046</v>
       </c>
@@ -6500,7 +6729,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2010</v>
       </c>
@@ -7044,7 +7273,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2044</v>
       </c>
@@ -7780,7 +8009,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>1913</v>
       </c>
@@ -7844,7 +8073,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2061</v>
       </c>
@@ -7876,7 +8105,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2184</v>
       </c>
@@ -8356,7 +8585,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2210</v>
       </c>
@@ -8388,7 +8617,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2065</v>
       </c>
@@ -8420,7 +8649,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2213</v>
       </c>
@@ -10116,7 +10345,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>1980</v>
       </c>
@@ -10148,7 +10377,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2008</v>
       </c>
@@ -10788,7 +11017,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>1992</v>
       </c>
@@ -11620,7 +11849,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>2535</v>
       </c>
@@ -12164,7 +12393,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>1990</v>
       </c>
@@ -12356,7 +12585,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>1998</v>
       </c>
@@ -12388,7 +12617,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>2002</v>
       </c>
@@ -13604,7 +13833,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>2624</v>
       </c>
@@ -13828,7 +14057,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>2615</v>
       </c>
@@ -14020,7 +14249,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>2000</v>
       </c>
@@ -14436,7 +14665,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>1986</v>
       </c>
@@ -14532,7 +14761,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>2734</v>
       </c>
@@ -15204,7 +15433,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>2331</v>
       </c>
@@ -15428,7 +15657,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>2599</v>
       </c>
@@ -16068,7 +16297,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>2778</v>
       </c>
@@ -16996,7 +17225,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>2712</v>
       </c>
@@ -17604,7 +17833,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>2868</v>
       </c>
@@ -17700,7 +17929,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>1987</v>
       </c>
@@ -17924,7 +18153,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>2382</v>
       </c>
@@ -18340,7 +18569,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>2194</v>
       </c>
@@ -18852,7 +19081,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>2912</v>
       </c>
@@ -18884,7 +19113,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>2913</v>
       </c>
@@ -18916,7 +19145,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>2914</v>
       </c>
@@ -19236,7 +19465,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>2932</v>
       </c>
@@ -20132,7 +20361,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>2946</v>
       </c>
@@ -20580,7 +20809,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>2935</v>
       </c>
@@ -20708,7 +20937,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>2489</v>
       </c>
@@ -20932,7 +21161,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>2006</v>
       </c>
@@ -21124,7 +21353,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>2484</v>
       </c>
@@ -21348,7 +21577,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>2754</v>
       </c>
@@ -21412,7 +21641,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>2001</v>
       </c>
@@ -21444,7 +21673,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>3016</v>
       </c>
@@ -21764,7 +21993,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>2895</v>
       </c>
@@ -22532,7 +22761,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>3144</v>
       </c>
@@ -22948,7 +23177,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>2958</v>
       </c>
@@ -23300,7 +23529,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>2101</v>
       </c>
@@ -23684,7 +23913,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>3216</v>
       </c>
@@ -25476,7 +25705,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>3292</v>
       </c>
@@ -25636,7 +25865,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>3146</v>
       </c>
@@ -25732,7 +25961,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>2281</v>
       </c>
@@ -25956,7 +26185,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>3336</v>
       </c>
@@ -26020,7 +26249,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>2404</v>
       </c>
@@ -26052,7 +26281,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>2426</v>
       </c>
@@ -26084,7 +26313,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>2449</v>
       </c>
@@ -26500,7 +26729,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734">
         <v>2223</v>
       </c>
@@ -26692,7 +26921,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740">
         <v>3395</v>
       </c>
@@ -26820,7 +27049,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744">
         <v>3408</v>
       </c>
@@ -26980,7 +27209,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749">
         <v>3411</v>
       </c>
@@ -27108,7 +27337,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753">
         <v>2965</v>
       </c>
@@ -27140,7 +27369,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754">
         <v>3131</v>
       </c>
@@ -27204,7 +27433,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756">
         <v>2894</v>
       </c>
@@ -29380,7 +29609,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824">
         <v>3514</v>
       </c>
@@ -29412,7 +29641,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825">
         <v>3515</v>
       </c>
@@ -29540,7 +29769,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829">
         <v>2047</v>
       </c>
@@ -29892,7 +30121,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840">
         <v>3130</v>
       </c>
@@ -30756,7 +30985,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867">
         <v>2910</v>
       </c>
@@ -31076,7 +31305,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877">
         <v>3601</v>
       </c>
@@ -31236,7 +31465,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882">
         <v>2878</v>
       </c>
@@ -31684,7 +31913,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896">
         <v>2448</v>
       </c>
@@ -32068,7 +32297,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908">
         <v>1981</v>
       </c>
@@ -32324,7 +32553,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916">
         <v>1982</v>
       </c>
@@ -33284,7 +33513,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946">
         <v>3405</v>
       </c>
@@ -33316,7 +33545,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947">
         <v>3406</v>
       </c>
@@ -33412,7 +33641,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950">
         <v>3132</v>
       </c>
@@ -33476,7 +33705,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952">
         <v>3694</v>
       </c>
@@ -35012,7 +35241,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000">
         <v>2248</v>
       </c>
@@ -35076,7 +35305,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002">
         <v>2014</v>
       </c>
@@ -35716,7 +35945,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1022">
         <v>2061</v>
       </c>
@@ -35844,7 +36073,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026">
         <v>2009</v>
       </c>
@@ -35876,7 +36105,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027">
         <v>2012</v>
       </c>
@@ -37156,7 +37385,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1067" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1067">
         <v>2251</v>
       </c>
@@ -38084,7 +38313,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1096" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1096">
         <v>1527</v>
       </c>
@@ -38116,7 +38345,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1097" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1097">
         <v>1843</v>
       </c>
@@ -38244,7 +38473,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1101">
         <v>2447</v>
       </c>
@@ -38340,7 +38569,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1104">
         <v>3476</v>
       </c>
@@ -39652,7 +39881,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1145">
         <v>3031</v>
       </c>
@@ -40324,7 +40553,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1166">
         <v>3898</v>
       </c>
@@ -40356,7 +40585,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1167">
         <v>3899</v>
       </c>
@@ -40388,7 +40617,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1168">
         <v>3900</v>
       </c>
@@ -41188,7 +41417,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1193">
         <v>3919</v>
       </c>
@@ -41892,7 +42121,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1215">
         <v>2383</v>
       </c>
@@ -42116,7 +42345,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1222">
         <v>3217</v>
       </c>
@@ -42532,7 +42761,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1235">
         <v>3932</v>
       </c>
@@ -44292,7 +44521,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1290">
         <v>3979</v>
       </c>
@@ -46948,7 +47177,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1373">
         <v>2004</v>
       </c>
@@ -47204,7 +47433,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1381">
         <v>3129</v>
       </c>
@@ -48036,7 +48265,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1407">
         <v>3933</v>
       </c>
@@ -48100,7 +48329,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1409">
         <v>4000</v>
       </c>
@@ -48228,7 +48457,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1413">
         <v>4052</v>
       </c>
@@ -48708,7 +48937,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1428">
         <v>3208</v>
       </c>
@@ -49732,7 +49961,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1460">
         <v>3999</v>
       </c>
@@ -50468,7 +50697,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1483" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1483">
         <v>4118</v>
       </c>
@@ -51844,7 +52073,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1526" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1526">
         <v>4142</v>
       </c>
@@ -51972,7 +52201,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1530" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1530">
         <v>4153</v>
       </c>
@@ -52740,7 +52969,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1554">
         <v>2607</v>
       </c>
@@ -52932,7 +53161,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1560">
         <v>3200</v>
       </c>
@@ -52964,7 +53193,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1561">
         <v>3201</v>
       </c>
@@ -53028,7 +53257,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1563">
         <v>3254</v>
       </c>
@@ -53508,7 +53737,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1578" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1578">
         <v>4051</v>
       </c>
@@ -53668,7 +53897,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1583">
         <v>4176</v>
       </c>
@@ -54916,7 +55145,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1622" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1622">
         <v>4204</v>
       </c>
@@ -55652,7 +55881,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1645" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1645">
         <v>4141</v>
       </c>
@@ -55780,7 +56009,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1649" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1649">
         <v>4220</v>
       </c>
@@ -55812,7 +56041,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1650" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1650">
         <v>4223</v>
       </c>
@@ -56228,7 +56457,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1663" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1663">
         <v>2893</v>
       </c>
@@ -56484,7 +56713,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1671" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1671">
         <v>4233</v>
       </c>
@@ -56740,7 +56969,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1679" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1679">
         <v>331</v>
       </c>
@@ -58404,7 +58633,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1731" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1731">
         <v>2739</v>
       </c>
@@ -58500,7 +58729,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1734" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1734">
         <v>4173</v>
       </c>
@@ -60100,7 +60329,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1784" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1784">
         <v>2187</v>
       </c>
@@ -61380,7 +61609,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1824" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1824">
         <v>2040</v>
       </c>
@@ -61412,7 +61641,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1825" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1825">
         <v>2067</v>
       </c>
@@ -66212,7 +66441,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="1975" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1975" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1975">
         <v>4125</v>
       </c>
@@ -68132,7 +68361,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2035" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2035" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2035">
         <v>2994</v>
       </c>
@@ -68164,7 +68393,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2036" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2036" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2036">
         <v>4302</v>
       </c>
@@ -69476,7 +69705,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2077" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2077" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2077">
         <v>2713</v>
       </c>
@@ -69508,7 +69737,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2078" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2078" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2078">
         <v>1979</v>
       </c>
@@ -69988,7 +70217,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2093" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2093" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2093">
         <v>2412</v>
       </c>
@@ -70308,7 +70537,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2103">
         <v>2352</v>
       </c>
@@ -70436,7 +70665,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2107">
         <v>4164</v>
       </c>
@@ -70628,7 +70857,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2113">
         <v>2381</v>
       </c>
@@ -72548,7 +72777,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2173">
         <v>2424</v>
       </c>
@@ -72676,7 +72905,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2177">
         <v>2425</v>
       </c>
@@ -72900,7 +73129,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2184">
         <v>4334</v>
       </c>
@@ -74784,7 +75013,7 @@
         <v>0</v>
       </c>
       <c r="I2242" s="2">
-        <f t="shared" ref="I2242:I2305" si="35">F2242 + G2242 - H2242</f>
+        <f t="shared" ref="I2242:I2272" si="35">F2242 + G2242 - H2242</f>
         <v>1000</v>
       </c>
     </row>
@@ -75364,7 +75593,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2261">
         <v>3005</v>
       </c>
@@ -75556,7 +75785,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2267">
         <v>4078</v>
       </c>
@@ -75588,7 +75817,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2268">
         <v>4079</v>
       </c>
@@ -75620,7 +75849,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2269">
         <v>4111</v>
       </c>
@@ -75749,18 +75978,21 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NQ+wA9HfgVDCVzEFtiSul5CV7CQndBBFEpg3W+z1uclys7W9xnlZQuaNQozfu8T7NHYd8e2WRiBnHvnrC580OA==" saltValue="zMbqiUFKn3i+ZYgInKjoNg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0" selectUnlockedCells="1"/>
   <conditionalFormatting sqref="I2:I1000">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>AND(A2&lt;&gt;"", I2&lt;100)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G999"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -81774,7 +82006,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Zaloga_Avtomatizirana.xlsx
+++ b/Zaloga_Avtomatizirana.xlsx
@@ -11,7 +11,9 @@
     <sheet name="ODPIS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="JULIJ 26" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TRENUTNA ZALOGA'!$A$1:$I$2272</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -77945,7 +77947,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="Cvn2wLBohqmXZH05hz65Ow==" formatRows="1" sort="1" spinCount="100000" hashValue="7dZhtl+j+qwImB1B7H31WLI047YXssuKEuR/5H0+QC3n49N/sTVe9xXhCuA/WsIEHGuGVtqR1WXrH/9NPKnsjA=="/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="Cvn2wLBohqmXZH05hz65Ow==" formatRows="1" sort="0" spinCount="100000" hashValue="7dZhtl+j+qwImB1B7H31WLI047YXssuKEuR/5H0+QC3n49N/sTVe9xXhCuA/WsIEHGuGVtqR1WXrH/9NPKnsjA=="/>
+  <autoFilter ref="A1:I2272"/>
   <conditionalFormatting sqref="I2:I1000">
     <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
       <formula>AND(A2&lt;&gt;"", I2&lt;100)</formula>
@@ -84180,7 +84183,6 @@
           <t xml:space="preserve">Dobavnica: 12345, Dobavitelj: </t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -84211,7 +84213,6 @@
           <t xml:space="preserve">Dobavnica: 12346, Dobavitelj: </t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -84242,7 +84243,6 @@
           <t xml:space="preserve">DN: , Oseba: </t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -84273,7 +84273,6 @@
           <t xml:space="preserve">DN: , Oseba: </t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
